--- a/apps/firefly/assets/docs/release-schedule.xlsx
+++ b/apps/firefly/assets/docs/release-schedule.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/andredavcev/Projects/theory/apps/assets-firefly/docs/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/andredavcev/Projects/theory/apps/firefly/assets/docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBF7E4C9-6810-1D42-91DA-D3AA658A5807}" xr6:coauthVersionLast="38" xr6:coauthVersionMax="38" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64746ECB-0978-1E44-8292-27C46AEFBF26}" xr6:coauthVersionLast="38" xr6:coauthVersionMax="38" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2500" yWindow="460" windowWidth="22720" windowHeight="18820" xr2:uid="{D9A7F54E-A8DF-8F44-8DA3-CE45AC6D884A}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="80">
   <si>
     <t>Version</t>
   </si>
@@ -262,6 +262,9 @@
   </si>
   <si>
     <t>Subscriptions Stream</t>
+  </si>
+  <si>
+    <t>Migrate To Bit</t>
   </si>
 </sst>
 </file>
@@ -623,7 +626,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E808F83-7B39-7A4C-8F08-E0AB4C8C7AD2}">
-  <dimension ref="B2:F57"/>
+  <dimension ref="B2:F58"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="2.6640625" customWidth="1"/>
@@ -901,97 +904,102 @@
     </row>
     <row r="46" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B46" t="s">
-        <v>19</v>
-      </c>
-      <c r="C46" t="s">
-        <v>10</v>
-      </c>
-      <c r="D46" t="s">
-        <v>49</v>
+        <v>79</v>
       </c>
     </row>
     <row r="47" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B47" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C47" t="s">
-        <v>11</v>
+        <v>10</v>
+      </c>
+      <c r="D47" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="48" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B48" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C48" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="49" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B49" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C49" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="50" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B50" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C50" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="51" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B51" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C51" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="52" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B52" t="s">
-        <v>73</v>
+        <v>24</v>
+      </c>
+      <c r="C52" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="53" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B53" t="s">
-        <v>25</v>
-      </c>
-      <c r="C53" t="s">
-        <v>16</v>
+        <v>73</v>
       </c>
     </row>
     <row r="54" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B54" t="s">
-        <v>74</v>
+        <v>25</v>
+      </c>
+      <c r="C54" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="55" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B55" t="s">
-        <v>52</v>
-      </c>
-      <c r="C55" t="s">
-        <v>53</v>
+        <v>74</v>
       </c>
     </row>
     <row r="56" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B56" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="C56" t="s">
-        <v>54</v>
-      </c>
-      <c r="D56" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
     </row>
     <row r="57" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B57" t="s">
+        <v>55</v>
+      </c>
+      <c r="C57" t="s">
+        <v>54</v>
+      </c>
+      <c r="D57" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="58" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B58" t="s">
         <v>57</v>
       </c>
-      <c r="C57" t="s">
+      <c r="C58" t="s">
         <v>59</v>
       </c>
     </row>

--- a/apps/firefly/assets/docs/release-schedule.xlsx
+++ b/apps/firefly/assets/docs/release-schedule.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11014"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11109"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/andredavcev/Projects/theory/apps/firefly/assets/docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64746ECB-0978-1E44-8292-27C46AEFBF26}" xr6:coauthVersionLast="38" xr6:coauthVersionMax="38" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CE5B4E9-B983-1240-AC7C-785ED48342B0}" xr6:coauthVersionLast="40" xr6:coauthVersionMax="40" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2500" yWindow="460" windowWidth="22720" windowHeight="18820" xr2:uid="{D9A7F54E-A8DF-8F44-8DA3-CE45AC6D884A}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="81">
   <si>
     <t>Version</t>
   </si>
@@ -265,6 +265,9 @@
   </si>
   <si>
     <t>Migrate To Bit</t>
+  </si>
+  <si>
+    <t>Firebase Test Lab</t>
   </si>
 </sst>
 </file>
@@ -626,7 +629,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E808F83-7B39-7A4C-8F08-E0AB4C8C7AD2}">
-  <dimension ref="B2:F58"/>
+  <dimension ref="B2:F59"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="2.6640625" customWidth="1"/>
@@ -860,146 +863,151 @@
     </row>
     <row r="39" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B39" t="s">
-        <v>17</v>
-      </c>
-      <c r="C39" t="s">
-        <v>8</v>
-      </c>
-      <c r="D39" t="s">
-        <v>31</v>
+        <v>80</v>
       </c>
     </row>
     <row r="40" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B40" t="s">
-        <v>50</v>
+        <v>17</v>
+      </c>
+      <c r="C40" t="s">
+        <v>8</v>
+      </c>
+      <c r="D40" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="41" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B41" t="s">
-        <v>29</v>
+        <v>50</v>
       </c>
     </row>
     <row r="42" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B42" t="s">
-        <v>48</v>
+        <v>29</v>
       </c>
     </row>
     <row r="43" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B43" t="s">
-        <v>18</v>
-      </c>
-      <c r="C43" t="s">
-        <v>9</v>
+        <v>48</v>
       </c>
     </row>
     <row r="44" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B44" t="s">
-        <v>64</v>
+        <v>18</v>
+      </c>
+      <c r="C44" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="45" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B45" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="46" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B46" t="s">
-        <v>79</v>
+        <v>66</v>
       </c>
     </row>
     <row r="47" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B47" t="s">
-        <v>19</v>
-      </c>
-      <c r="C47" t="s">
-        <v>10</v>
-      </c>
-      <c r="D47" t="s">
-        <v>49</v>
+        <v>79</v>
       </c>
     </row>
     <row r="48" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B48" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C48" t="s">
-        <v>11</v>
+        <v>10</v>
+      </c>
+      <c r="D48" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="49" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B49" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C49" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="50" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B50" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C50" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="51" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B51" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C51" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="52" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B52" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C52" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="53" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B53" t="s">
-        <v>73</v>
+        <v>24</v>
+      </c>
+      <c r="C53" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="54" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B54" t="s">
-        <v>25</v>
-      </c>
-      <c r="C54" t="s">
-        <v>16</v>
+        <v>73</v>
       </c>
     </row>
     <row r="55" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B55" t="s">
-        <v>74</v>
+        <v>25</v>
+      </c>
+      <c r="C55" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="56" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B56" t="s">
-        <v>52</v>
-      </c>
-      <c r="C56" t="s">
-        <v>53</v>
+        <v>74</v>
       </c>
     </row>
     <row r="57" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B57" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="C57" t="s">
-        <v>54</v>
-      </c>
-      <c r="D57" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
     </row>
     <row r="58" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B58" t="s">
+        <v>55</v>
+      </c>
+      <c r="C58" t="s">
+        <v>54</v>
+      </c>
+      <c r="D58" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="59" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B59" t="s">
         <v>57</v>
       </c>
-      <c r="C58" t="s">
+      <c r="C59" t="s">
         <v>59</v>
       </c>
     </row>
